--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.4%</t>
+          <t>444.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.7%</t>
+          <t>-600.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.4%</t>
+          <t>-84.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.4%</t>
+          <t>-278.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.3%</t>
+          <t>-276.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-204.1%</t>
+          <t>-203.6%</t>
         </is>
       </c>
     </row>
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.744935368203436</v>
+        <v>3.721939150619249</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.451145275514751</v>
+        <v>-4.389597211859382</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9578683482121244</v>
+        <v>0.982487573674272</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.532841265190954</v>
+        <v>-0.5237582016811708</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.4189781236172</v>
+        <v>2.42442796172307</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>115.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.2%</t>
+          <t>444.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-600.5%</t>
+          <t>-607.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.6%</t>
+          <t>-84.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.0%</t>
+          <t>-280.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-276.4%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-203.6%</t>
+          <t>-204.4%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.721939150619249</v>
+        <v>3.723066344039157</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.389597211859382</v>
+        <v>-4.458932115212697</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.982487573674272</v>
+        <v>0.9547536123329459</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5237582016811708</v>
+        <v>-0.5380330963152333</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.42442796172307</v>
+        <v>2.415863024942632</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.1%</t>
+          <t>440.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-627.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.3%</t>
+          <t>-83.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.7%</t>
+          <t>-288.8%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679501961319289</v>
+        <v>-4.880965529633156</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9548758666013244</v>
+        <v>0.8742904392757778</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790438213960538</v>
+        <v>-4.991901782274405</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9105128394316222</v>
+        <v>0.8299274121060756</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.993464791503771</v>
+        <v>-5.194928359817638</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8324335936342346</v>
+        <v>0.751848166308688</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.835539192568478</v>
+        <v>-5.037002760882345</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9057762196404842</v>
+        <v>0.8251907923149373</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.983860446379607</v>
+        <v>-5.185324014693474</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8413939886898929</v>
+        <v>0.7608085613643465</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.985043531030668</v>
+        <v>-5.186507099344535</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8326965302739944</v>
+        <v>0.7521111029484473</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.861915824036585</v>
+        <v>-5.063379392350452</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8824994861047291</v>
+        <v>0.801914058779182</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.769105342585725</v>
+        <v>-4.970568910899592</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8488963705764385</v>
+        <v>0.7683109432508917</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.720542290364695</v>
+        <v>-4.922005858678562</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8701950673894514</v>
+        <v>0.7896096400639043</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.607871072128445</v>
+        <v>-4.809334640442312</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9103392631956744</v>
+        <v>0.8297538358701275</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.495494070945772</v>
+        <v>-4.696957639259639</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9607813594994108</v>
+        <v>0.8801959321738639</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.693728639832503</v>
+        <v>-4.89519220814637</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8929847337132575</v>
+        <v>0.8123993063877106</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.776729920857782</v>
+        <v>-4.978193489171649</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6981399413037992</v>
+        <v>0.6175545139782523</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.617535648801205</v>
+        <v>-4.818999217115072</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8819673108456356</v>
+        <v>0.8013818835200885</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.704134231782308</v>
+        <v>-4.905597800096175</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8618409037555175</v>
+        <v>0.7812554764299704</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46493,10 +46493,10 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.665750569224157</v>
+        <v>-4.867214137538024</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8746138101211465</v>
+        <v>0.7940283827955996</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46516,10 +46516,10 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.488634239188991</v>
+        <v>-4.690097807502858</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9421893709805154</v>
+        <v>0.8616039436549683</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.723066344039157</v>
+        <v>3.417890977701297</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.458932115212697</v>
+        <v>-4.660395683526565</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9547536123329459</v>
+        <v>0.8741681850073988</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-42.0%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>115.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.2%</t>
+          <t>444.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.6%</t>
+          <t>-607.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-83.7%</t>
+          <t>-84.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.8%</t>
+          <t>-280.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-204.4%</t>
+          <t>-177.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1956"/>
+  <dimension ref="A1:G1957"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.880965529633156</v>
+        <v>-4.679501961319289</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8742904392757778</v>
+        <v>0.9548758666013244</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.991901782274405</v>
+        <v>-4.790438213960538</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8299274121060756</v>
+        <v>0.9105128394316222</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.194928359817638</v>
+        <v>-4.993464791503771</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.751848166308688</v>
+        <v>0.8324335936342346</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.037002760882345</v>
+        <v>-4.835539192568478</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8251907923149373</v>
+        <v>0.9057762196404842</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.185324014693474</v>
+        <v>-4.983860446379607</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7608085613643465</v>
+        <v>0.8413939886898929</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.186507099344535</v>
+        <v>-4.985043531030668</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7521111029484473</v>
+        <v>0.8326965302739944</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.063379392350452</v>
+        <v>-4.861915824036585</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.801914058779182</v>
+        <v>0.8824994861047291</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.970568910899592</v>
+        <v>-4.769105342585725</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7683109432508917</v>
+        <v>0.8488963705764385</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.922005858678562</v>
+        <v>-4.720542290364695</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7896096400639043</v>
+        <v>0.8701950673894514</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.809334640442312</v>
+        <v>-4.607871072128445</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8297538358701275</v>
+        <v>0.9103392631956744</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.696957639259639</v>
+        <v>-4.495494070945772</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8801959321738639</v>
+        <v>0.9607813594994108</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.89519220814637</v>
+        <v>-4.693728639832503</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8123993063877106</v>
+        <v>0.8929847337132575</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.978193489171649</v>
+        <v>-4.776729920857782</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6175545139782523</v>
+        <v>0.6981399413037992</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.818999217115072</v>
+        <v>-4.617535648801205</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8013818835200885</v>
+        <v>0.8819673108456356</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.905597800096175</v>
+        <v>-4.704134231782308</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7812554764299704</v>
+        <v>0.8618409037555175</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46493,10 +46493,10 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.867214137538024</v>
+        <v>-4.665750569224157</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7940283827955996</v>
+        <v>0.8746138101211465</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46516,10 +46516,10 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.690097807502858</v>
+        <v>-4.488634239188991</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8616039436549683</v>
+        <v>0.9421893709805154</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46533,22 +46533,45 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.417890977701297</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.660395683526565</v>
+        <v>-4.458932115212697</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8741681850073988</v>
+        <v>0.9547536123329459</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
       </c>
       <c r="G1956" t="n">
         <v>2.415863024942632</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="2" t="n">
+        <v>45419</v>
+      </c>
+      <c r="B1957" t="n">
+        <v>3.722885290408254</v>
+      </c>
+      <c r="C1957" t="n">
+        <v>2.69643814401117</v>
+      </c>
+      <c r="D1957" t="n">
+        <v>-4.458932115212697</v>
+      </c>
+      <c r="E1957" t="n">
+        <v>0.9547536123329459</v>
+      </c>
+      <c r="F1957" t="n">
+        <v>-0.5380330963152333</v>
+      </c>
+      <c r="G1957" t="n">
+        <v>2.689501940997538</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>134.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.1%</t>
+          <t>444.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-614.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.3%</t>
+          <t>-60.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.7%</t>
+          <t>-283.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.1%</t>
+          <t>-156.0%</t>
         </is>
       </c>
     </row>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.078565586985051</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2788432933073643</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.741209520764524</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.494957461272048</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.1102805942014431</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.741209520764524</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-7.871634471801893</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.03013151934181568</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.217509293786701</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.1723818829900439</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.379651564249794</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2388338711202804</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.676312906059993</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3537194319151515</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.109662014170228</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5310853796936486</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.492663402912859</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.684388036512285</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.65006228312598</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.7447760726261032</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.00959260562998</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.8832378983296536</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.33599263429499</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.005881889838481</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.55514160236919</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.090499726446392</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.55145067741278</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.089023356463827</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.75570885274264</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.165213429477131</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-10.97374662437382</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.247945983645165</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-10.90027679270637</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.203186349484764</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.07540121009292</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.258680895691866</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.30985330410741</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.359680898199257</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.59765714864464</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.481474626788129</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.82748159580847</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.572288615815102</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.05951051554473</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.662406455080493</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.00749500157592</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.637609913806567</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.14916684330004</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.695753877394957</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.0995759988752</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.660864129460151</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-11.90042389163811</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.594254420211994</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.67457873891869</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.49433728608802</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.5500000825811</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.443366678996924</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.60289537062539</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.461891020052532</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.31898663969664</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.342593823442395</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.24762024708699</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.323784528792402</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-10.98378337988292</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.228133263223681</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-10.71654157901452</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.123071103375696</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74602975292243</v>
+        <v>-10.61863454033803</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.13516668791232</v>
+        <v>-1.08420860287856</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72207621194648</v>
+        <v>-10.59468099936208</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.124916765376443</v>
+        <v>-1.073958680342684</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45801627362368</v>
+        <v>-10.33062106103928</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.032553106209077</v>
+        <v>-0.9815950211753171</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.750936650118842</v>
+        <v>-9.623541437534442</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7525082904674432</v>
+        <v>-0.7015502054336831</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.710752351752651</v>
+        <v>-9.583357139168251</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7360909472331256</v>
+        <v>-0.6851328621993655</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.630682556214847</v>
+        <v>-9.503287343630447</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7046962077972467</v>
+        <v>-0.6537381227634871</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.397201333985247</v>
+        <v>-9.269806121400848</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6033792900675548</v>
+        <v>-0.5524212050337947</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.217492803841374</v>
+        <v>-9.090097591256974</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5343880883229644</v>
+        <v>-0.4834300032892047</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.085217330210487</v>
+        <v>-8.957822117626087</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4861104121235824</v>
+        <v>-0.4351523270898228</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.894617655537333</v>
+        <v>-8.767222442952933</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4070554815666845</v>
+        <v>-0.3560973965329244</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.645617856853752</v>
+        <v>-8.518222644269352</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2945492208695932</v>
+        <v>-0.2435911358358331</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.751207846626857</v>
+        <v>-8.623812634042457</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4647611463780539</v>
+        <v>-0.4138030613442938</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.769942748745454</v>
+        <v>-8.642547536161054</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4237107653484062</v>
+        <v>-0.3727526803146461</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.622002707337854</v>
+        <v>-8.494607494753454</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4844136714735341</v>
+        <v>-0.433455586439774</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.597774070948882</v>
+        <v>-8.470378858364482</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.483436203171423</v>
+        <v>-0.4324781181376633</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.55422566417819</v>
+        <v>-8.426830451593791</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.47297745255824</v>
+        <v>-0.4220193675244799</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.312077270724332</v>
+        <v>-8.184682058139932</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3616557407955536</v>
+        <v>-0.3106976557617935</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.248847898955985</v>
+        <v>-8.121452686371585</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3418318716290196</v>
+        <v>-0.2908737865952595</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.125556764138855</v>
+        <v>-7.998161551554454</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2950173236915905</v>
+        <v>-0.2440592386578304</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.104407565235412</v>
+        <v>-7.977012352651011</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2788566658928886</v>
+        <v>-0.2278985808591276</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.860642123251968</v>
+        <v>-7.733246910667567</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1855697807524601</v>
+        <v>-0.1346116957186996</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.596614056058709</v>
+        <v>-7.469218843474307</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07783423995514038</v>
+        <v>-0.0268761549213794</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.346763662109634</v>
+        <v>-7.219368449525232</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0148479926081917</v>
+        <v>0.06580607764195223</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.170871569642202</v>
+        <v>-7.0434763570578</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08880395311581335</v>
+        <v>0.1397620381495739</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.999425106619738</v>
+        <v>-6.872029894035337</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1707100443793523</v>
+        <v>0.2216681294131129</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.774392106950915</v>
+        <v>-6.646996894366514</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2597437218631784</v>
+        <v>0.3107018068969394</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.559757729314509</v>
+        <v>-6.432362516730107</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3502922739720584</v>
+        <v>0.4012503590058194</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.46675768810861</v>
+        <v>-6.339362475524209</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3686865492382134</v>
+        <v>0.419644634271974</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.22632719130375</v>
+        <v>-6.098931978719349</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4666018245850352</v>
+        <v>0.5175599096187957</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.983536383654305</v>
+        <v>-5.856141171069903</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5676474614796336</v>
+        <v>0.6186055465133942</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.867596534029119</v>
+        <v>-5.740201321444718</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6147019852470477</v>
+        <v>0.6656600702808082</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.624940945605957</v>
+        <v>-5.497545733021555</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7087622918363063</v>
+        <v>0.7597203768700669</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.404920147568946</v>
+        <v>-5.277524934984545</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7983496480617247</v>
+        <v>0.8493077330954852</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.205671517664137</v>
+        <v>-5.078276305079735</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8939432828254716</v>
+        <v>0.9449013678592322</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.046156414144767</v>
+        <v>-4.918761201560366</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9588951686735214</v>
+        <v>1.009853253707282</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.90148426904503</v>
+        <v>-4.774089056460628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.026852129274856</v>
+        <v>1.077810214308617</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.961359096402722</v>
+        <v>-4.833963883818321</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.988939689733205</v>
+        <v>1.039897774766966</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.874559598623714</v>
+        <v>-4.747164386039312</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.046059982167374</v>
+        <v>1.097018067201135</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.87702930508552</v>
+        <v>-4.749634092501118</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.045144500956064</v>
+        <v>1.096102585989825</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.94539949140953</v>
+        <v>-4.818004278825128</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.028803348901162</v>
+        <v>1.079761433934923</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823983061783053</v>
+        <v>-4.696587849198652</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.067806629383644</v>
+        <v>1.118764714417405</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854976221111759</v>
+        <v>-4.727581008527357</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8801189306925488</v>
+        <v>0.9310770157263093</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679501961319289</v>
+        <v>-4.753570317048754</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9548758666013244</v>
+        <v>0.9252485243095383</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790438213960538</v>
+        <v>-4.864506569690003</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9105128394316222</v>
+        <v>0.8808854971398363</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.993464791503771</v>
+        <v>-5.067533147233236</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8324335936342346</v>
+        <v>0.8028062513424485</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.835539192568478</v>
+        <v>-4.909607548297943</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9057762196404842</v>
+        <v>0.8761488773486981</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.983860446379607</v>
+        <v>-5.057928802109072</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8413939886898929</v>
+        <v>0.811766646398107</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.985043531030668</v>
+        <v>-5.059111886760133</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8326965302739944</v>
+        <v>0.8030691879822078</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.861915824036585</v>
+        <v>-4.93598417976605</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8824994861047291</v>
+        <v>0.8528721438129427</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.769105342585725</v>
+        <v>-4.843173698315191</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8488963705764385</v>
+        <v>0.8192690282846522</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.720542290364695</v>
+        <v>-4.794610646094161</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8701950673894514</v>
+        <v>0.8405677250976651</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.607871072128445</v>
+        <v>-4.681939427857911</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9103392631956744</v>
+        <v>0.8807119209038881</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.495494070945772</v>
+        <v>-4.569562426675238</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9607813594994108</v>
+        <v>0.9311540172076245</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.693728639832503</v>
+        <v>-4.767796995561969</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8929847337132575</v>
+        <v>0.8633573914214712</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.776729920857782</v>
+        <v>-4.850798276587247</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6981399413037992</v>
+        <v>0.6685125990120129</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.617535648801205</v>
+        <v>-4.691604004530671</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8819673108456356</v>
+        <v>0.8523399685538493</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.704134231782308</v>
+        <v>-4.778202587511774</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8618409037555175</v>
+        <v>0.8322135614637309</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46493,10 +46493,10 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.665750569224157</v>
+        <v>-4.739818924953623</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8746138101211465</v>
+        <v>0.8449864678293602</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46516,10 +46516,10 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.488634239188991</v>
+        <v>-4.562702594918457</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9421893709805154</v>
+        <v>0.912562028688729</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.458932115212697</v>
+        <v>-4.533000470942163</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9547536123329459</v>
+        <v>0.9251262700411595</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.722885290408254</v>
+        <v>3.818566154425206</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.69643814401117</v>
+        <v>2.907348707799174</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.458932115212697</v>
+        <v>-4.533000470942163</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9547536123329459</v>
+        <v>0.9251262700411595</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5380330963152333</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.689501940997538</v>
+        <v>2.900412504785542</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-56.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.4%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.9%</t>
+          <t>-593.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.7%</t>
+          <t>-275.3%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.078565586985051</v>
+        <v>-7.069332414007068</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2788432933073643</v>
+        <v>0.2825365624985579</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.741209520764524</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.494957461272048</v>
+        <v>-7.485724288294065</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1102805942014431</v>
+        <v>0.1139738633926362</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.741209520764524</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.871634471801893</v>
+        <v>-7.86240129882391</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.03013151934181568</v>
+        <v>-0.02643825015062262</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.217509293786701</v>
+        <v>-8.208276120808719</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1723818829900439</v>
+        <v>-0.1686886137988513</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.379651564249794</v>
+        <v>-8.370418391271812</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2388338711202804</v>
+        <v>-0.2351406019290874</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.676312906059993</v>
+        <v>-8.66707973308201</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3537194319151515</v>
+        <v>-0.3500261627239585</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.109662014170228</v>
+        <v>-9.100428841192246</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5310853796936486</v>
+        <v>-0.5273921105024559</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.492663402912859</v>
+        <v>-9.483430229934877</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.684388036512285</v>
+        <v>-0.6806947673210924</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.65006228312598</v>
+        <v>-9.640829110147997</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7447760726261032</v>
+        <v>-0.7410828034349106</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.00959260562998</v>
+        <v>-10.000359432652</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8832378983296536</v>
+        <v>-0.879544629138461</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.33599263429499</v>
+        <v>-10.32675946131701</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.005881889838481</v>
+        <v>-1.002188620647289</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.55514160236919</v>
+        <v>-10.54590842939121</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.090499726446392</v>
+        <v>-1.086806457255199</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.55145067741278</v>
+        <v>-10.5422175044348</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.089023356463827</v>
+        <v>-1.085330087272635</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.75570885274264</v>
+        <v>-10.74647567976466</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.165213429477131</v>
+        <v>-1.161520160285938</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.97374662437382</v>
+        <v>-10.96451345139584</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.247945983645165</v>
+        <v>-1.244252714453972</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.90027679270637</v>
+        <v>-10.89104361972839</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.203186349484764</v>
+        <v>-1.199493080293572</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.07540121009292</v>
+        <v>-11.06616803711493</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.258680895691866</v>
+        <v>-1.254987626500673</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.30985330410741</v>
+        <v>-11.30062013112942</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.359680898199257</v>
+        <v>-1.355987629008065</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.59765714864464</v>
+        <v>-11.58842397566666</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.481474626788129</v>
+        <v>-1.477781357596936</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.82748159580847</v>
+        <v>-11.81824842283049</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.572288615815102</v>
+        <v>-1.568595346623909</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.05951051554473</v>
+        <v>-12.05027734256675</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.662406455080493</v>
+        <v>-1.6587131858893</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.00749500157592</v>
+        <v>-11.99826182859794</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.637609913806567</v>
+        <v>-1.633916644615374</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.14916684330004</v>
+        <v>-12.13993367032206</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.695753877394957</v>
+        <v>-1.692060608203763</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.0995759988752</v>
+        <v>-12.09034282589722</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.660864129460151</v>
+        <v>-1.657170860268958</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.90042389163811</v>
+        <v>-11.89119071866012</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.594254420211994</v>
+        <v>-1.590561151020801</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.67457873891869</v>
+        <v>-11.66534556594071</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.49433728608802</v>
+        <v>-1.490644016896827</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.5500000825811</v>
+        <v>-11.54076690960312</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.443366678996924</v>
+        <v>-1.439673409805732</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.60289537062539</v>
+        <v>-11.59366219764741</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.461891020052532</v>
+        <v>-1.458197750861339</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.31898663969664</v>
+        <v>-11.30975346671866</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.342593823442395</v>
+        <v>-1.338900554251203</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.24762024708699</v>
+        <v>-11.23838707410901</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.323784528792402</v>
+        <v>-1.320091259601209</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.98378337988292</v>
+        <v>-10.97455020690494</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.228133263223681</v>
+        <v>-1.224439994032488</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.71654157901452</v>
+        <v>-10.70730840603654</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.123071103375696</v>
+        <v>-1.119377834184503</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.61863454033803</v>
+        <v>-10.60940136736005</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.08420860287856</v>
+        <v>-1.080515333687368</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.59468099936208</v>
+        <v>-10.58544782638409</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.073958680342684</v>
+        <v>-1.070265411151491</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.33062106103928</v>
+        <v>-10.3213878880613</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9815950211753171</v>
+        <v>-0.977901751984124</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.623541437534442</v>
+        <v>-9.61430826455646</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7015502054336831</v>
+        <v>-0.6978569362424905</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.583357139168251</v>
+        <v>-9.574123966190269</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6851328621993655</v>
+        <v>-0.6814395930081729</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.503287343630447</v>
+        <v>-9.494054170652465</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6537381227634871</v>
+        <v>-0.650044853572294</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.269806121400848</v>
+        <v>-9.260572948422865</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5524212050337947</v>
+        <v>-0.548727935842602</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.090097591256974</v>
+        <v>-9.080864418278992</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4834300032892047</v>
+        <v>-0.4797367340980117</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.957822117626087</v>
+        <v>-8.948588944648105</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4351523270898228</v>
+        <v>-0.4314590578986297</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.767222442952933</v>
+        <v>-8.757989269974951</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3560973965329244</v>
+        <v>-0.3524041273417318</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.518222644269352</v>
+        <v>-8.50898947129137</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2435911358358331</v>
+        <v>-0.2398978666446405</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.623812634042457</v>
+        <v>-8.614579461064475</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4138030613442938</v>
+        <v>-0.4101097921531007</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.642547536161054</v>
+        <v>-8.633314363183072</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3727526803146461</v>
+        <v>-0.3690594111234535</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.494607494753454</v>
+        <v>-8.485374321775472</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.433455586439774</v>
+        <v>-0.4297623172485814</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.470378858364482</v>
+        <v>-8.4611456853865</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4324781181376633</v>
+        <v>-0.4287848489464703</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.426830451593791</v>
+        <v>-8.417597278615808</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4220193675244799</v>
+        <v>-0.4183260983332868</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.184682058139932</v>
+        <v>-8.17544888516195</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3106976557617935</v>
+        <v>-0.3070043865706005</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.121452686371585</v>
+        <v>-8.112219513393603</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2908737865952595</v>
+        <v>-0.2871805174040665</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.998161551554454</v>
+        <v>-7.988928378576472</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2440592386578304</v>
+        <v>-0.2403659694666374</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.977012352651011</v>
+        <v>-7.967779179673029</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2278985808591276</v>
+        <v>-0.224205311667935</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.733246910667567</v>
+        <v>-7.724013737689584</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1346116957186996</v>
+        <v>-0.1309184265275065</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.469218843474307</v>
+        <v>-7.459985670496325</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.0268761549213794</v>
+        <v>-0.02318288573018679</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.219368449525232</v>
+        <v>-7.21013527654725</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06580607764195223</v>
+        <v>0.06949934683314529</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.0434763570578</v>
+        <v>-7.034243184079818</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1397620381495739</v>
+        <v>0.1434553073407669</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.872029894035337</v>
+        <v>-6.862796721057355</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2216681294131129</v>
+        <v>0.2253613986043059</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.646996894366514</v>
+        <v>-6.637763721388532</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3107018068969394</v>
+        <v>0.314395076088132</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.432362516730107</v>
+        <v>-6.423129343752125</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4012503590058194</v>
+        <v>0.404943628197012</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.339362475524209</v>
+        <v>-6.330129302546227</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.419644634271974</v>
+        <v>0.423337903463167</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.098931978719349</v>
+        <v>-6.089698805741366</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5175599096187957</v>
+        <v>0.5212531788099883</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.856141171069903</v>
+        <v>-5.846907998091921</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6186055465133942</v>
+        <v>0.6222988157045868</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.740201321444718</v>
+        <v>-5.730968148466736</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6656600702808082</v>
+        <v>0.6693533394720013</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.497545733021555</v>
+        <v>-5.488312560043573</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7597203768700669</v>
+        <v>0.7634136460612595</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.277524934984545</v>
+        <v>-5.268291762006562</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8493077330954852</v>
+        <v>0.8530010022866779</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.078276305079735</v>
+        <v>-5.069043132101753</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9449013678592322</v>
+        <v>0.9485946370504248</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.918761201560366</v>
+        <v>-4.909528028582383</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.009853253707282</v>
+        <v>1.013546522898475</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.774089056460628</v>
+        <v>-4.764855883482646</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.077810214308617</v>
+        <v>1.08150348349981</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.833963883818321</v>
+        <v>-4.824730710840338</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.039897774766966</v>
+        <v>1.043591043958159</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.747164386039312</v>
+        <v>-4.73793121306133</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.097018067201135</v>
+        <v>1.100711336392328</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.749634092501118</v>
+        <v>-4.740400919523136</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.096102585989825</v>
+        <v>1.099795855181018</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.818004278825128</v>
+        <v>-4.808771105847146</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.079761433934923</v>
+        <v>1.083454703126116</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.696587849198652</v>
+        <v>-4.68735467622067</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.118764714417405</v>
+        <v>1.122457983608597</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.727581008527357</v>
+        <v>-4.718347835549375</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9310770157263093</v>
+        <v>0.9347702849175021</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.753570317048754</v>
+        <v>-4.542873575756905</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9252485243095383</v>
+        <v>1.009527220826278</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.76502074769545</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.864506569690003</v>
+        <v>-4.653809828398154</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8808854971398363</v>
+        <v>0.9651641936565758</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.067533147233236</v>
+        <v>-4.856836405941388</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8028062513424485</v>
+        <v>0.887084947859188</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.909607548297943</v>
+        <v>-4.698910807006095</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8761488773486981</v>
+        <v>0.9604275738654375</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.057928802109072</v>
+        <v>-4.847232060817223</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.811766646398107</v>
+        <v>0.8960453429148465</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.059111886760133</v>
+        <v>-4.848415145468284</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8030691879822078</v>
+        <v>0.8873478844989477</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.93598417976605</v>
+        <v>-4.725287438474201</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8528721438129427</v>
+        <v>0.9371508403296827</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279503</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.843173698315191</v>
+        <v>-4.632476957023341</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8192690282846522</v>
+        <v>0.9035477248013921</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030431</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.794610646094161</v>
+        <v>-4.583913904802311</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8405677250976651</v>
+        <v>0.9248464216144048</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942743</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.681939427857911</v>
+        <v>-4.471242686566061</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8807119209038881</v>
+        <v>0.964990617420628</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268541</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.569562426675238</v>
+        <v>-4.358865685383388</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9311540172076245</v>
+        <v>1.015432713724364</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.767796995561969</v>
+        <v>-4.557100254270119</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8633573914214712</v>
+        <v>0.9476360879382111</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.850798276587247</v>
+        <v>-4.640101535295398</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6685125990120129</v>
+        <v>0.7527912955287528</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.682712735199273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.691604004530671</v>
+        <v>-4.480907263238821</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8523399685538493</v>
+        <v>0.936618665070589</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660773</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.778202587511774</v>
+        <v>-4.567505846219924</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8322135614637309</v>
+        <v>0.9164922579804708</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383429</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.739818924953623</v>
+        <v>-4.529122183661773</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8449864678293602</v>
+        <v>0.9292651643461001</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.562702594918457</v>
+        <v>-4.352005853626607</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.912562028688729</v>
+        <v>0.9968407252054687</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263906</v>
+        <v>3.741324873263908</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.533000470942163</v>
+        <v>-4.322303729650313</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9251262700411595</v>
+        <v>1.009404966557899</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.818566154425206</v>
+        <v>3.818566154425207</v>
       </c>
       <c r="C1957" t="n">
         <v>2.907348707799174</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.533000470942163</v>
+        <v>-4.322303729650313</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9251262700411595</v>
+        <v>1.009404966557899</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.5380330963152333</v>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-38.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.1%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>134.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.8%</t>
+          <t>-606.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-275.3%</t>
+          <t>-280.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-154.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-281.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-207.5%</t>
         </is>
       </c>
     </row>
@@ -46559,19 +46559,19 @@
         <v>3.818566154425207</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.907348707799174</v>
+        <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.322303729650313</v>
+        <v>-4.448454745071316</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.009404966557899</v>
+        <v>0.9527315356959127</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5380330963152333</v>
+        <v>-0.5786155435458317</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.900412504785542</v>
+        <v>2.385300531910687</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240507.xlsx
+++ b/tame_output/ON/bt/strategyON_20240507.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>114.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.3%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.4%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>440.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.4%</t>
+          <t>-606.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.9%</t>
+          <t>-280.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.7%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-281.9%</t>
+          <t>-261.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-207.5%</t>
+          <t>-195.4%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.069332414007068</v>
+        <v>-7.205960799569449</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2825365624985579</v>
+        <v>0.2278852082736051</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.741209520764524</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.485724288294065</v>
+        <v>-7.622352673856446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1139738633926362</v>
+        <v>0.05932250916768389</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.741209520764524</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.86240129882391</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02643825015062262</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.208276120808719</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1686886137988513</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.370418391271812</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2351406019290874</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.66707973308201</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3500261627239585</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.100428841192246</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5273921105024559</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.483430229934877</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6806947673210924</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.640829110147997</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7410828034349106</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.000359432652</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.879544629138461</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.32675946131701</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.002188620647289</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.54590842939121</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.086806457255199</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.5422175044348</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.085330087272635</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.74647567976466</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.161520160285938</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.96451345139584</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.244252714453972</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.89104361972839</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.199493080293572</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.06616803711493</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.254987626500673</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.30062013112942</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.355987629008065</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.58842397566666</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.477781357596936</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.81824842283049</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.568595346623909</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.05027734256675</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.6587131858893</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.99826182859794</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.633916644615374</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.13993367032206</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.692060608203763</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.09034282589722</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.657170860268958</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.89119071866012</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.590561151020801</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.66534556594071</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.490644016896827</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.54076690960312</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.439673409805732</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.59366219764741</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.458197750861339</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.30975346671866</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.338900554251203</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.23838707410901</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.320091259601209</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.97455020690494</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.224439994032488</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.70730840603654</v>
+        <v>-10.84393679159892</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.119377834184503</v>
+        <v>-1.174029188409456</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60940136736005</v>
+        <v>-10.74602975292243</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.080515333687368</v>
+        <v>-1.13516668791232</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.58544782638409</v>
+        <v>-10.72207621194648</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.070265411151491</v>
+        <v>-1.124916765376443</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.3213878880613</v>
+        <v>-10.45801627362368</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.977901751984124</v>
+        <v>-1.032553106209077</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.61430826455646</v>
+        <v>-9.750936650118842</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6978569362424905</v>
+        <v>-0.7525082904674432</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.574123966190269</v>
+        <v>-9.710752351752651</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6814395930081729</v>
+        <v>-0.7360909472331256</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.494054170652465</v>
+        <v>-9.630682556214847</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.650044853572294</v>
+        <v>-0.7046962077972467</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.260572948422865</v>
+        <v>-9.397201333985247</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.548727935842602</v>
+        <v>-0.6033792900675548</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.080864418278992</v>
+        <v>-9.217492803841374</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4797367340980117</v>
+        <v>-0.5343880883229644</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.948588944648105</v>
+        <v>-9.085217330210487</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4314590578986297</v>
+        <v>-0.4861104121235824</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.757989269974951</v>
+        <v>-8.894617655537333</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3524041273417318</v>
+        <v>-0.4070554815666845</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.50898947129137</v>
+        <v>-8.645617856853752</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2398978666446405</v>
+        <v>-0.2945492208695932</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.614579461064475</v>
+        <v>-8.751207846626857</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4101097921531007</v>
+        <v>-0.4647611463780539</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.633314363183072</v>
+        <v>-8.769942748745454</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3690594111234535</v>
+        <v>-0.4237107653484062</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.485374321775472</v>
+        <v>-8.622002707337854</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4297623172485814</v>
+        <v>-0.4844136714735341</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.4611456853865</v>
+        <v>-8.597774070948882</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4287848489464703</v>
+        <v>-0.483436203171423</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.417597278615808</v>
+        <v>-8.55422566417819</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4183260983332868</v>
+        <v>-0.47297745255824</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.17544888516195</v>
+        <v>-8.312077270724332</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3070043865706005</v>
+        <v>-0.3616557407955536</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.112219513393603</v>
+        <v>-8.248847898955985</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2871805174040665</v>
+        <v>-0.3418318716290196</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.988928378576472</v>
+        <v>-8.125556764138855</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2403659694666374</v>
+        <v>-0.2950173236915905</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.967779179673029</v>
+        <v>-8.104407565235412</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.224205311667935</v>
+        <v>-0.2788566658928886</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.724013737689584</v>
+        <v>-7.860642123251968</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1309184265275065</v>
+        <v>-0.1855697807524601</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.459985670496325</v>
+        <v>-7.596614056058709</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.02318288573018679</v>
+        <v>-0.07783423995514038</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.21013527654725</v>
+        <v>-7.346763662109634</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.06949934683314529</v>
+        <v>0.0148479926081917</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.034243184079818</v>
+        <v>-7.170871569642202</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1434553073407669</v>
+        <v>0.08880395311581335</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.862796721057355</v>
+        <v>-6.999425106619738</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2253613986043059</v>
+        <v>0.1707100443793523</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.637763721388532</v>
+        <v>-6.774392106950915</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.314395076088132</v>
+        <v>0.2597437218631784</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.423129343752125</v>
+        <v>-6.559757729314509</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.404943628197012</v>
+        <v>0.3502922739720584</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.330129302546227</v>
+        <v>-6.46675768810861</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.423337903463167</v>
+        <v>0.3686865492382134</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.089698805741366</v>
+        <v>-6.22632719130375</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5212531788099883</v>
+        <v>0.4666018245850352</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.846907998091921</v>
+        <v>-6.154084623132555</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6222988157045868</v>
+        <v>0.4994281656883333</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.730968148466736</v>
+        <v>-6.03814477350737</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6693533394720013</v>
+        <v>0.5464826894557473</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.488312560043573</v>
+        <v>-5.795489185084207</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7634136460612595</v>
+        <v>0.640542996045006</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.268291762006562</v>
+        <v>-5.575468387047197</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8530010022866779</v>
+        <v>0.7301303522704243</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.069043132101753</v>
+        <v>-5.376219757142388</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9485946370504248</v>
+        <v>0.8257239870341713</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.909528028582383</v>
+        <v>-5.216704653623018</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.013546522898475</v>
+        <v>0.8906758728822211</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.764855883482646</v>
+        <v>-5.07203250852328</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.08150348349981</v>
+        <v>0.9586328334835557</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.824730710840338</v>
+        <v>-5.131907335880973</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.043591043958159</v>
+        <v>0.9207203939419046</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.73793121306133</v>
+        <v>-5.045107838101965</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.100711336392328</v>
+        <v>0.9778406863760742</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.740400919523136</v>
+        <v>-5.047577544563771</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.099795855181018</v>
+        <v>0.9769252051647639</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.808771105847146</v>
+        <v>-5.115947730887781</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.083454703126116</v>
+        <v>0.9605840531098617</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.68735467622067</v>
+        <v>-4.994531301261304</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.122457983608597</v>
+        <v>0.9995873335923438</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.718347835549375</v>
+        <v>-5.02552446059001</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9347702849175021</v>
+        <v>0.8118996349012484</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.542873575756905</v>
+        <v>-4.85005020079754</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.009527220826278</v>
+        <v>0.886656570810024</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769545</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.653809828398154</v>
+        <v>-4.960986453438789</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9651641936565758</v>
+        <v>0.8422935436403221</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581296</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.856836405941388</v>
+        <v>-5.164013030982022</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.887084947859188</v>
+        <v>0.7642142978429343</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734165</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.698910807006095</v>
+        <v>-5.006087432046729</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9604275738654375</v>
+        <v>0.8375569238491838</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212301</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.847232060817223</v>
+        <v>-5.154408685857858</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8960453429148465</v>
+        <v>0.7731746928985928</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786049</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.848415145468284</v>
+        <v>-5.155591770508918</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8873478844989477</v>
+        <v>0.764477234482694</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273194</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.725287438474201</v>
+        <v>-5.032464063514835</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9371508403296827</v>
+        <v>0.8142801903134287</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279503</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.632476957023341</v>
+        <v>-4.939653582063976</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9035477248013921</v>
+        <v>0.7806770747851384</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030431</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.583913904802311</v>
+        <v>-4.891090529842946</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9248464216144048</v>
+        <v>0.801975771598151</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942743</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.471242686566061</v>
+        <v>-4.778419311606696</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.964990617420628</v>
+        <v>0.8421199674043742</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268541</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.358865685383388</v>
+        <v>-4.666042310424023</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.015432713724364</v>
+        <v>0.8925620637081106</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968866</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.557100254270119</v>
+        <v>-4.864276879310753</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9476360879382111</v>
+        <v>0.8247654379219573</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175327</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.640101535295398</v>
+        <v>-4.947278160336032</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7527912955287528</v>
+        <v>0.629920645512499</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199273</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.480907263238821</v>
+        <v>-4.788083888279456</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.936618665070589</v>
+        <v>0.8137480150543352</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660773</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.567505846219924</v>
+        <v>-4.874682471260559</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9164922579804708</v>
+        <v>0.7936216079642171</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383429</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.529122183661773</v>
+        <v>-4.836298808702407</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9292651643461001</v>
+        <v>0.8063945143298463</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002489</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.352005853626607</v>
+        <v>-4.659182478667241</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9968407252054687</v>
+        <v>0.873970075189215</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263908</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.322303729650313</v>
+        <v>-4.629480354690948</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.009404966557899</v>
+        <v>0.8865343165416455</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.818566154425207</v>
+        <v>3.422844493121747</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.448454745071316</v>
+        <v>-4.44476339788096</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9527315356959127</v>
+        <v>0.9542080745720549</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5786155435458317</v>
+        <v>-0.3767253260861917</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.385300531910687</v>
+        <v>2.506434662386472</v>
       </c>
     </row>
   </sheetData>
